--- a/examples/ISO/DataTable_A.xlsx
+++ b/examples/ISO/DataTable_A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMIDER\運用マニュアル・ツール\メタデータ\ExcelToXml\完成版コード\動作試験\ISO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DFEB63-079E-4CCC-9CE9-6155EC51C94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9D75CD-F679-4EA7-86A0-9208262989E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{02E672FE-9466-4421-A9D7-2018D514ED3D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02E672FE-9466-4421-A9D7-2018D514ED3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Element Name</t>
     <phoneticPr fontId="1"/>
@@ -112,13 +112,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作成者</t>
-    <rPh sb="0" eb="3">
-      <t>サクセイシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -134,11 +127,32 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>dataset</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字コード</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>utf8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種別</t>
+    <rPh sb="0" eb="2">
+      <t>シュベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>XML作成者</t>
+    <rPh sb="3" eb="6">
+      <t>サクセイシャ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -519,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E28054-8828-447C-930F-8F764D093E62}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.25" style="1" bestFit="1" customWidth="1"/>
@@ -533,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -553,16 +567,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3"/>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -583,41 +597,51 @@
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A9" s="3"/>
       <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D10" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A9:A10"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
